--- a/Reports/07_Takada_Ayumi_作業報告.xlsx
+++ b/Reports/07_Takada_Ayumi_作業報告.xlsx
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="73">
   <si>
     <t>■進級制作　作業報告書</t>
     <rPh sb="1" eb="3">
@@ -3298,6 +3298,33 @@
     </rPh>
     <rPh sb="3" eb="4">
       <t>アユミ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・TICKETS - 3 都市のアセット検索 TO-DO → 進行中 → 完了済
+・TICKETS - 14 都市のアセット検索 TO-DO → 進行中 → 保留（マップ端っこが落ちる、道路側の整備が不完全。しかし、実際のゲーム操作でどの程度まで続くかわからないためいったん保留。）
+・TICKETS - 16 都市のアセット検索 TO-DO → 進行中（残：獲得時のパーティクル）</t>
+    <rPh sb="13" eb="15">
+      <t>トシ</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>ケンサク</t>
+    </rPh>
+    <rPh sb="31" eb="34">
+      <t>シンコウチュウ</t>
+    </rPh>
+    <rPh sb="37" eb="39">
+      <t>カンリョウ</t>
+    </rPh>
+    <rPh sb="39" eb="40">
+      <t>ズ</t>
+    </rPh>
+    <rPh sb="79" eb="81">
+      <t>ホリュウ</t>
+    </rPh>
+    <rPh sb="178" eb="179">
+      <t>ノコ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -4341,7 +4368,9 @@
       <c r="B5" s="13" t="s">
         <v>70</v>
       </c>
-      <c r="C5" s="14"/>
+      <c r="C5" s="14" t="s">
+        <v>72</v>
+      </c>
       <c r="D5" s="15"/>
       <c r="E5" s="13"/>
     </row>

--- a/Reports/07_Takada_Ayumi_作業報告.xlsx
+++ b/Reports/07_Takada_Ayumi_作業報告.xlsx
@@ -3288,10 +3288,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>・GitHubDesktopのインストール</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>高田 歩</t>
     <rPh sb="0" eb="2">
       <t>タカダ</t>
@@ -3302,28 +3298,33 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>・TICKETS - 3 都市のアセット検索 TO-DO → 進行中 → 完了済
+    <t>・GitHubDesktopのインストール</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・GitHubDesktopのインストール
+・TICKETS - 3 都市のアセット検索 TO-DO → 進行中 → 完了済
 ・TICKETS - 14 都市のアセット検索 TO-DO → 進行中 → 保留（マップ端っこが落ちる、道路側の整備が不完全。しかし、実際のゲーム操作でどの程度まで続くかわからないためいったん保留。）
 ・TICKETS - 16 都市のアセット検索 TO-DO → 進行中（残：獲得時のパーティクル）</t>
-    <rPh sb="13" eb="15">
+    <rPh sb="35" eb="37">
       <t>トシ</t>
     </rPh>
-    <rPh sb="20" eb="22">
+    <rPh sb="42" eb="44">
       <t>ケンサク</t>
     </rPh>
-    <rPh sb="31" eb="34">
+    <rPh sb="53" eb="56">
       <t>シンコウチュウ</t>
     </rPh>
-    <rPh sb="37" eb="39">
+    <rPh sb="59" eb="61">
       <t>カンリョウ</t>
     </rPh>
-    <rPh sb="39" eb="40">
+    <rPh sb="61" eb="62">
       <t>ズ</t>
     </rPh>
-    <rPh sb="79" eb="81">
+    <rPh sb="101" eb="103">
       <t>ホリュウ</t>
     </rPh>
-    <rPh sb="178" eb="179">
+    <rPh sb="200" eb="201">
       <t>ノコ</t>
     </rPh>
     <phoneticPr fontId="1"/>
@@ -4328,7 +4329,7 @@
         <v>1</v>
       </c>
       <c r="E2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -4366,7 +4367,7 @@
         <v>46120</v>
       </c>
       <c r="B5" s="13" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C5" s="14" t="s">
         <v>72</v>

--- a/Reports/07_Takada_Ayumi_作業報告.xlsx
+++ b/Reports/07_Takada_Ayumi_作業報告.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\student\Documents\assignment2-uic-tickets\Reports\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\teacher\Documents\GitHub\assignment2-uic-tickets\Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="75">
   <si>
     <t>■進級制作　作業報告書</t>
     <rPh sb="1" eb="3">
@@ -3326,6 +3326,66 @@
     </rPh>
     <rPh sb="200" eb="201">
       <t>ノコ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>蒲池</t>
+    <rPh sb="0" eb="2">
+      <t>カマチ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・翌日の予定の記載もお願いします。
+・操作感がわからないとフィールドがどの程度必要か決めづらいですね。ゲームコアの作成に最低限必要な素材が集められているのであれば、実装の方を進めていきましょう。</t>
+    <rPh sb="1" eb="3">
+      <t>ヨクジツ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ヨテイ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>キサイ</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>ネガ</t>
+    </rPh>
+    <rPh sb="19" eb="22">
+      <t>ソウサカン</t>
+    </rPh>
+    <rPh sb="37" eb="39">
+      <t>テイド</t>
+    </rPh>
+    <rPh sb="39" eb="41">
+      <t>ヒツヨウ</t>
+    </rPh>
+    <rPh sb="42" eb="43">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="57" eb="59">
+      <t>サクセイ</t>
+    </rPh>
+    <rPh sb="60" eb="63">
+      <t>サイテイゲン</t>
+    </rPh>
+    <rPh sb="63" eb="65">
+      <t>ヒツヨウ</t>
+    </rPh>
+    <rPh sb="66" eb="68">
+      <t>ソザイ</t>
+    </rPh>
+    <rPh sb="69" eb="70">
+      <t>アツ</t>
+    </rPh>
+    <rPh sb="82" eb="84">
+      <t>ジッソウ</t>
+    </rPh>
+    <rPh sb="85" eb="86">
+      <t>ホウ</t>
+    </rPh>
+    <rPh sb="87" eb="88">
+      <t>スス</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -4372,8 +4432,12 @@
       <c r="C5" s="14" t="s">
         <v>72</v>
       </c>
-      <c r="D5" s="15"/>
-      <c r="E5" s="13"/>
+      <c r="D5" s="15" t="s">
+        <v>73</v>
+      </c>
+      <c r="E5" s="14" t="s">
+        <v>74</v>
+      </c>
     </row>
     <row r="6" spans="1:5" ht="108" customHeight="1">
       <c r="A6" s="12"/>

--- a/Reports/07_Takada_Ayumi_作業報告.xlsx
+++ b/Reports/07_Takada_Ayumi_作業報告.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12120" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="11370" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="サンプル" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="78">
   <si>
     <t>■進級制作　作業報告書</t>
     <rPh sb="1" eb="3">
@@ -3326,6 +3326,116 @@
     </rPh>
     <rPh sb="200" eb="201">
       <t>ノコ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>蒲池</t>
+    <rPh sb="0" eb="2">
+      <t>カマチ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・翌日の予定の記載もお願いします。
+・操作感がわからないとフィールドがどの程度必要か決めづらいですね。ゲームコアの作成に最低限必要な素材が集められているのであれば、実装の方を進めていきましょう。</t>
+    <rPh sb="1" eb="3">
+      <t>ヨクジツ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ヨテイ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>キサイ</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>ネガ</t>
+    </rPh>
+    <rPh sb="19" eb="22">
+      <t>ソウサカン</t>
+    </rPh>
+    <rPh sb="37" eb="39">
+      <t>テイド</t>
+    </rPh>
+    <rPh sb="39" eb="41">
+      <t>ヒツヨウ</t>
+    </rPh>
+    <rPh sb="42" eb="43">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="57" eb="59">
+      <t>サクセイ</t>
+    </rPh>
+    <rPh sb="60" eb="63">
+      <t>サイテイゲン</t>
+    </rPh>
+    <rPh sb="63" eb="65">
+      <t>ヒツヨウ</t>
+    </rPh>
+    <rPh sb="66" eb="68">
+      <t>ソザイ</t>
+    </rPh>
+    <rPh sb="69" eb="70">
+      <t>アツ</t>
+    </rPh>
+    <rPh sb="82" eb="84">
+      <t>ジッソウ</t>
+    </rPh>
+    <rPh sb="85" eb="86">
+      <t>ホウ</t>
+    </rPh>
+    <rPh sb="87" eb="88">
+      <t>スス</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・TICKETS - 16 コインのプログラム 進行中 → 完了済
+・TICKETS - 19 車のアセット検索 TO-DO → 進行中 → 完了済
+・TICKETS - 14 都市の当たり判定 保留 → 進行中（残：当たり判定漏れのチェック）
+・TICKETS - 18 ゲームマップデザイン TO-DO</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・コインのパーティクル調整
+・残りのチケットを作業が終わり次第とりかかる</t>
+    <rPh sb="11" eb="13">
+      <t>チョウセイ</t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t>ノコ</t>
+    </rPh>
+    <rPh sb="23" eb="25">
+      <t>サギョウ</t>
+    </rPh>
+    <rPh sb="26" eb="27">
+      <t>オ</t>
+    </rPh>
+    <rPh sb="29" eb="31">
+      <t>シダイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・都市の当たり判定のチェックの続き
+・ゲームマップデザインに取り掛かる</t>
+    <rPh sb="1" eb="3">
+      <t>トシ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>ハンテイ</t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t>ツヅ</t>
+    </rPh>
+    <rPh sb="30" eb="31">
+      <t>ト</t>
+    </rPh>
+    <rPh sb="32" eb="33">
+      <t>カ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -4372,19 +4482,33 @@
       <c r="C5" s="14" t="s">
         <v>72</v>
       </c>
-      <c r="D5" s="15"/>
-      <c r="E5" s="13"/>
+      <c r="D5" s="15" t="s">
+        <v>73</v>
+      </c>
+      <c r="E5" s="14" t="s">
+        <v>74</v>
+      </c>
     </row>
     <row r="6" spans="1:5" ht="108" customHeight="1">
-      <c r="A6" s="12"/>
-      <c r="B6" s="14"/>
-      <c r="C6" s="14"/>
+      <c r="A6" s="12">
+        <v>46121</v>
+      </c>
+      <c r="B6" s="14" t="s">
+        <v>76</v>
+      </c>
+      <c r="C6" s="14" t="s">
+        <v>75</v>
+      </c>
       <c r="D6" s="15"/>
       <c r="E6" s="13"/>
     </row>
     <row r="7" spans="1:5" ht="108" customHeight="1">
-      <c r="A7" s="12"/>
-      <c r="B7" s="14"/>
+      <c r="A7" s="12">
+        <v>46122</v>
+      </c>
+      <c r="B7" s="14" t="s">
+        <v>77</v>
+      </c>
       <c r="C7" s="14"/>
       <c r="D7" s="15"/>
       <c r="E7" s="13"/>

--- a/Reports/07_Takada_Ayumi_作業報告.xlsx
+++ b/Reports/07_Takada_Ayumi_作業報告.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="11370" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="11370"/>
   </bookViews>
   <sheets>
     <sheet name="サンプル" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="79">
   <si>
     <t>■進級制作　作業報告書</t>
     <rPh sb="1" eb="3">
@@ -3437,6 +3437,10 @@
     <rPh sb="32" eb="33">
       <t>カ</t>
     </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -3901,6 +3905,12 @@
       </c>
     </row>
     <row r="2" spans="1:5">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>78</v>
+      </c>
       <c r="D2" s="4" t="s">
         <v>1</v>
       </c>

--- a/Reports/07_Takada_Ayumi_作業報告.xlsx
+++ b/Reports/07_Takada_Ayumi_作業報告.xlsx
@@ -5,11 +5,11 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\student\Documents\assignment2-uic-tickets\Reports\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\teacher\Documents\GitHub\assignment2-uic-tickets\Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="11370"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="11370" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="サンプル" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="81">
   <si>
     <t>■進級制作　作業報告書</t>
     <rPh sb="1" eb="3">
@@ -3441,6 +3441,49 @@
   </si>
   <si>
     <t xml:space="preserve"> </t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>蒲池</t>
+    <rPh sb="0" eb="2">
+      <t>カマチ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・タスク進行がわかりやすくて良いです
+・TICKETS-18 がTO-DO とのことですが、何か作業はしましたか？
+　しているなら進行中に、無いなら、翌日orそれ以降の作業予定に入れておきましょう</t>
+    <rPh sb="4" eb="6">
+      <t>シンコウ</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>イ</t>
+    </rPh>
+    <rPh sb="46" eb="47">
+      <t>ナニ</t>
+    </rPh>
+    <rPh sb="48" eb="50">
+      <t>サギョウ</t>
+    </rPh>
+    <rPh sb="65" eb="68">
+      <t>シンコウチュウ</t>
+    </rPh>
+    <rPh sb="70" eb="71">
+      <t>ナ</t>
+    </rPh>
+    <rPh sb="75" eb="77">
+      <t>ヨクジツ</t>
+    </rPh>
+    <rPh sb="81" eb="83">
+      <t>イコウ</t>
+    </rPh>
+    <rPh sb="84" eb="88">
+      <t>サギョウヨテイ</t>
+    </rPh>
+    <rPh sb="89" eb="90">
+      <t>イ</t>
+    </rPh>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -4509,8 +4552,12 @@
       <c r="C6" s="14" t="s">
         <v>75</v>
       </c>
-      <c r="D6" s="15"/>
-      <c r="E6" s="13"/>
+      <c r="D6" s="15" t="s">
+        <v>79</v>
+      </c>
+      <c r="E6" s="14" t="s">
+        <v>80</v>
+      </c>
     </row>
     <row r="7" spans="1:5" ht="108" customHeight="1">
       <c r="A7" s="12">

--- a/Reports/07_Takada_Ayumi_作業報告.xlsx
+++ b/Reports/07_Takada_Ayumi_作業報告.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="11370"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="11370" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="サンプル" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="83">
   <si>
     <t>■進級制作　作業報告書</t>
     <rPh sb="1" eb="3">
@@ -3390,6 +3390,53 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
+    <t>・コインのパーティクル調整
+・残りのチケットを作業が終わり次第とりかかる</t>
+    <rPh sb="11" eb="13">
+      <t>チョウセイ</t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t>ノコ</t>
+    </rPh>
+    <rPh sb="23" eb="25">
+      <t>サギョウ</t>
+    </rPh>
+    <rPh sb="26" eb="27">
+      <t>オ</t>
+    </rPh>
+    <rPh sb="29" eb="31">
+      <t>シダイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・都市の当たり判定のチェックの続き
+・ゲームマップデザインに取り掛かる</t>
+    <rPh sb="1" eb="3">
+      <t>トシ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>ハンテイ</t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t>ツヅ</t>
+    </rPh>
+    <rPh sb="30" eb="31">
+      <t>ト</t>
+    </rPh>
+    <rPh sb="32" eb="33">
+      <t>カ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
     <t>・TICKETS - 16 コインのプログラム 進行中 → 完了済
 ・TICKETS - 19 車のアセット検索 TO-DO → 進行中 → 完了済
 ・TICKETS - 14 都市の当たり判定 保留 → 進行中（残：当たり判定漏れのチェック）
@@ -3397,50 +3444,34 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>・コインのパーティクル調整
-・残りのチケットを作業が終わり次第とりかかる</t>
-    <rPh sb="11" eb="13">
-      <t>チョウセイ</t>
-    </rPh>
-    <rPh sb="15" eb="16">
-      <t>ノコ</t>
-    </rPh>
-    <rPh sb="23" eb="25">
-      <t>サギョウ</t>
-    </rPh>
-    <rPh sb="26" eb="27">
-      <t>オ</t>
-    </rPh>
-    <rPh sb="29" eb="31">
-      <t>シダイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>・都市の当たり判定のチェックの続き
-・ゲームマップデザインに取り掛かる</t>
-    <rPh sb="1" eb="3">
-      <t>トシ</t>
-    </rPh>
-    <rPh sb="4" eb="5">
-      <t>ア</t>
-    </rPh>
-    <rPh sb="7" eb="9">
-      <t>ハンテイ</t>
-    </rPh>
-    <rPh sb="15" eb="16">
+    <t>・タスク進行がわかりやすくて良いです。
+・TICKETS-18 がTO-DO とのことですが、何か作業はしましたか？
+　しているなら進行中に、無いなら、翌日orそれ以降の作業予定に入れておきましょう。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t xml:space="preserve">・TICKETS - 18 ゲームマップデザイン TO-DO → 進行中 → 完了
+・TICKETS - 14 都市の当たり判定 進行中 → 完了
+・TICKETS - 35 ゴミ箱を見やすいように光の柱をつける TO-DO → 進行中 → 完了
+・TICKETS - 29 スタート画面UI TO-DO → 進行中（残：タイトル画面制作）
+</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・スタート画面UIの続き</t>
+    <rPh sb="5" eb="7">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="10" eb="11">
       <t>ツヅ</t>
     </rPh>
-    <rPh sb="30" eb="31">
-      <t>ト</t>
-    </rPh>
-    <rPh sb="32" eb="33">
-      <t>カ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t xml:space="preserve"> </t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>α版</t>
+    <rPh sb="0" eb="2">
+      <t>アルファバン</t>
+    </rPh>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -3909,7 +3940,7 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D2" s="4" t="s">
         <v>1</v>
@@ -4432,19 +4463,19 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E36"/>
+  <dimension ref="A1:F36"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="2" max="3" width="58.625" customWidth="1"/>
     <col min="5" max="5" width="42.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:6">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:5">
+    <row r="2" spans="1:6">
       <c r="D2" s="4" t="s">
         <v>1</v>
       </c>
@@ -4452,7 +4483,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="3" spans="1:5">
+    <row r="3" spans="1:6">
       <c r="A3" s="3" t="s">
         <v>3</v>
       </c>
@@ -4469,7 +4500,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="108" customHeight="1">
+    <row r="4" spans="1:6" ht="108" customHeight="1">
       <c r="A4" s="17">
         <v>46119</v>
       </c>
@@ -4482,7 +4513,7 @@
       <c r="D4" s="10"/>
       <c r="E4" s="11"/>
     </row>
-    <row r="5" spans="1:5" ht="108" customHeight="1">
+    <row r="5" spans="1:6" ht="108" customHeight="1">
       <c r="A5" s="12">
         <v>46120</v>
       </c>
@@ -4499,87 +4530,108 @@
         <v>74</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="108" customHeight="1">
+    <row r="6" spans="1:6" ht="108" customHeight="1">
       <c r="A6" s="12">
         <v>46121</v>
       </c>
       <c r="B6" s="14" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C6" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="D6" s="15"/>
-      <c r="E6" s="13"/>
-    </row>
-    <row r="7" spans="1:5" ht="108" customHeight="1">
+        <v>78</v>
+      </c>
+      <c r="D6" s="15" t="s">
+        <v>73</v>
+      </c>
+      <c r="E6" s="14" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="108" customHeight="1">
       <c r="A7" s="12">
         <v>46122</v>
       </c>
       <c r="B7" s="14" t="s">
-        <v>77</v>
-      </c>
-      <c r="C7" s="14"/>
+        <v>76</v>
+      </c>
+      <c r="C7" s="14" t="s">
+        <v>80</v>
+      </c>
       <c r="D7" s="15"/>
       <c r="E7" s="13"/>
     </row>
-    <row r="8" spans="1:5" ht="108" customHeight="1">
-      <c r="A8" s="12"/>
-      <c r="B8" s="14"/>
+    <row r="8" spans="1:6" ht="108" customHeight="1">
+      <c r="A8" s="12">
+        <v>46125</v>
+      </c>
+      <c r="B8" s="14" t="s">
+        <v>81</v>
+      </c>
       <c r="C8" s="14"/>
       <c r="D8" s="15"/>
       <c r="E8" s="13"/>
     </row>
-    <row r="9" spans="1:5" ht="108" customHeight="1">
-      <c r="A9" s="12"/>
+    <row r="9" spans="1:6" ht="108" customHeight="1">
+      <c r="A9" s="12">
+        <v>46126</v>
+      </c>
       <c r="B9" s="14"/>
       <c r="C9" s="14"/>
       <c r="D9" s="15"/>
       <c r="E9" s="13"/>
     </row>
-    <row r="10" spans="1:5" ht="108" customHeight="1">
-      <c r="A10" s="12"/>
+    <row r="10" spans="1:6" ht="108" customHeight="1">
+      <c r="A10" s="12">
+        <v>46127</v>
+      </c>
       <c r="B10" s="14"/>
       <c r="C10" s="14"/>
       <c r="D10" s="15"/>
       <c r="E10" s="13"/>
     </row>
-    <row r="11" spans="1:5" ht="108" customHeight="1">
-      <c r="A11" s="12"/>
+    <row r="11" spans="1:6" ht="108" customHeight="1">
+      <c r="A11" s="12">
+        <v>46128</v>
+      </c>
       <c r="B11" s="14"/>
       <c r="C11" s="14"/>
       <c r="D11" s="15"/>
       <c r="E11" s="13"/>
     </row>
-    <row r="12" spans="1:5" ht="108" customHeight="1">
-      <c r="A12" s="12"/>
+    <row r="12" spans="1:6" ht="108" customHeight="1">
+      <c r="A12" s="12">
+        <v>46129</v>
+      </c>
       <c r="B12" s="14"/>
       <c r="C12" s="14"/>
       <c r="D12" s="15"/>
       <c r="E12" s="13"/>
-    </row>
-    <row r="13" spans="1:5" ht="108" customHeight="1">
+      <c r="F12" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" ht="108" customHeight="1">
       <c r="A13" s="12"/>
       <c r="B13" s="14"/>
       <c r="C13" s="14"/>
       <c r="D13" s="15"/>
       <c r="E13" s="13"/>
     </row>
-    <row r="14" spans="1:5" ht="108" customHeight="1">
+    <row r="14" spans="1:6" ht="108" customHeight="1">
       <c r="A14" s="12"/>
       <c r="B14" s="14"/>
       <c r="C14" s="14"/>
       <c r="D14" s="15"/>
       <c r="E14" s="13"/>
     </row>
-    <row r="15" spans="1:5" ht="108" customHeight="1">
+    <row r="15" spans="1:6" ht="108" customHeight="1">
       <c r="A15" s="12"/>
       <c r="B15" s="14"/>
       <c r="C15" s="14"/>
       <c r="D15" s="15"/>
       <c r="E15" s="13"/>
     </row>
-    <row r="16" spans="1:5" ht="108" customHeight="1">
+    <row r="16" spans="1:6" ht="108" customHeight="1">
       <c r="A16" s="12"/>
       <c r="B16" s="14"/>
       <c r="C16" s="14"/>

--- a/Reports/07_Takada_Ayumi_作業報告.xlsx
+++ b/Reports/07_Takada_Ayumi_作業報告.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="11370" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="11370"/>
   </bookViews>
   <sheets>
     <sheet name="サンプル" sheetId="1" r:id="rId1"/>
@@ -3936,9 +3936,6 @@
       </c>
     </row>
     <row r="2" spans="1:5">
-      <c r="A2">
-        <v>1</v>
-      </c>
       <c r="B2" t="s">
         <v>77</v>
       </c>

--- a/Reports/07_Takada_Ayumi_作業報告.xlsx
+++ b/Reports/07_Takada_Ayumi_作業報告.xlsx
@@ -3936,6 +3936,9 @@
       </c>
     </row>
     <row r="2" spans="1:5">
+      <c r="A2">
+        <v>1</v>
+      </c>
       <c r="B2" t="s">
         <v>77</v>
       </c>

--- a/Reports/07_Takada_Ayumi_作業報告.xlsx
+++ b/Reports/07_Takada_Ayumi_作業報告.xlsx
@@ -5,11 +5,11 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\student\Documents\assignment2-uic-tickets\Reports\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\teacher\Documents\GitHub\assignment2-uic-tickets\Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="11370"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="11370" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="サンプル" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="85">
   <si>
     <t>■進級制作　作業報告書</t>
     <rPh sb="1" eb="3">
@@ -3471,6 +3471,29 @@
     <t>α版</t>
     <rPh sb="0" eb="2">
       <t>アルファバン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>蒲池</t>
+    <rPh sb="0" eb="2">
+      <t>カマチ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・作業環境の構築ができているようであれば、GitHub の方に作業内容をUPしていくようにしましょう。</t>
+    <rPh sb="1" eb="5">
+      <t>サギョウカンキョウ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>コウチク</t>
+    </rPh>
+    <rPh sb="29" eb="30">
+      <t>ホウ</t>
+    </rPh>
+    <rPh sb="31" eb="35">
+      <t>サギョウナイヨウ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -4557,8 +4580,12 @@
       <c r="C7" s="14" t="s">
         <v>80</v>
       </c>
-      <c r="D7" s="15"/>
-      <c r="E7" s="13"/>
+      <c r="D7" s="15" t="s">
+        <v>83</v>
+      </c>
+      <c r="E7" s="13" t="s">
+        <v>84</v>
+      </c>
     </row>
     <row r="8" spans="1:6" ht="108" customHeight="1">
       <c r="A8" s="12">

--- a/Reports/07_Takada_Ayumi_作業報告.xlsx
+++ b/Reports/07_Takada_Ayumi_作業報告.xlsx
@@ -5,11 +5,11 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\teacher\Documents\GitHub\assignment2-uic-tickets\Reports\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\student\Documents\assignment2-uic-tickets\Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="11370" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="11370"/>
   </bookViews>
   <sheets>
     <sheet name="サンプル" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="87">
   <si>
     <t>■進級制作　作業報告書</t>
     <rPh sb="1" eb="3">
@@ -3450,6 +3450,46 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
+    <t>・スタート画面UIの続き</t>
+    <rPh sb="5" eb="7">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>ツヅ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>α版</t>
+    <rPh sb="0" eb="2">
+      <t>アルファバン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>蒲池</t>
+    <rPh sb="0" eb="2">
+      <t>カマチ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・作業環境の構築ができているようであれば、GitHub の方に作業内容をUPしていくようにしましょう。</t>
+    <rPh sb="1" eb="5">
+      <t>サギョウカンキョウ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>コウチク</t>
+    </rPh>
+    <rPh sb="29" eb="30">
+      <t>ホウ</t>
+    </rPh>
+    <rPh sb="31" eb="35">
+      <t>サギョウナイヨウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
     <t xml:space="preserve">・TICKETS - 18 ゲームマップデザイン TO-DO → 進行中 → 完了
 ・TICKETS - 14 都市の当たり判定 進行中 → 完了
 ・TICKETS - 35 ゴミ箱を見やすいように光の柱をつける TO-DO → 進行中 → 完了
@@ -3458,43 +3498,34 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>・スタート画面UIの続き</t>
-    <rPh sb="5" eb="7">
+    <t>・TICKETS - 29 スタート画面UI TO-DO → 進行中 → 完了
+・TICKETS - 16 コインのプログラム 完了 → 進行中 → 完了（当たり判定などの修正）
+・TICKETS - 36 ゲームマップデザイン２ TO-DO → 進行中</t>
+    <rPh sb="18" eb="20">
       <t>ガメン</t>
     </rPh>
-    <rPh sb="10" eb="11">
-      <t>ツヅ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>α版</t>
-    <rPh sb="0" eb="2">
-      <t>アルファバン</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>蒲池</t>
-    <rPh sb="0" eb="2">
-      <t>カマチ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>・作業環境の構築ができているようであれば、GitHub の方に作業内容をUPしていくようにしましょう。</t>
-    <rPh sb="1" eb="5">
-      <t>サギョウカンキョウ</t>
-    </rPh>
-    <rPh sb="6" eb="8">
-      <t>コウチク</t>
-    </rPh>
-    <rPh sb="29" eb="30">
-      <t>ホウ</t>
-    </rPh>
-    <rPh sb="31" eb="35">
-      <t>サギョウナイヨウ</t>
-    </rPh>
+    <rPh sb="64" eb="66">
+      <t>カンリョウ</t>
+    </rPh>
+    <rPh sb="69" eb="72">
+      <t>シンコウチュウ</t>
+    </rPh>
+    <rPh sb="75" eb="77">
+      <t>カンリョウ</t>
+    </rPh>
+    <rPh sb="78" eb="79">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="81" eb="83">
+      <t>ハンテイ</t>
+    </rPh>
+    <rPh sb="86" eb="88">
+      <t>シュウセイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・ゲームマップデザイン２</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -3959,9 +3990,6 @@
       </c>
     </row>
     <row r="2" spans="1:5">
-      <c r="A2">
-        <v>1</v>
-      </c>
       <c r="B2" t="s">
         <v>77</v>
       </c>
@@ -4578,13 +4606,13 @@
         <v>76</v>
       </c>
       <c r="C7" s="14" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="D7" s="15" t="s">
+        <v>82</v>
+      </c>
+      <c r="E7" s="13" t="s">
         <v>83</v>
-      </c>
-      <c r="E7" s="13" t="s">
-        <v>84</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="108" customHeight="1">
@@ -4592,9 +4620,11 @@
         <v>46125</v>
       </c>
       <c r="B8" s="14" t="s">
-        <v>81</v>
-      </c>
-      <c r="C8" s="14"/>
+        <v>80</v>
+      </c>
+      <c r="C8" s="14" t="s">
+        <v>85</v>
+      </c>
       <c r="D8" s="15"/>
       <c r="E8" s="13"/>
     </row>
@@ -4602,7 +4632,9 @@
       <c r="A9" s="12">
         <v>46126</v>
       </c>
-      <c r="B9" s="14"/>
+      <c r="B9" s="14" t="s">
+        <v>86</v>
+      </c>
       <c r="C9" s="14"/>
       <c r="D9" s="15"/>
       <c r="E9" s="13"/>
@@ -4634,7 +4666,7 @@
       <c r="D12" s="15"/>
       <c r="E12" s="13"/>
       <c r="F12" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="108" customHeight="1">

--- a/Reports/07_Takada_Ayumi_作業報告.xlsx
+++ b/Reports/07_Takada_Ayumi_作業報告.xlsx
@@ -5,11 +5,11 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\student\Documents\assignment2-uic-tickets\Reports\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\teacher\Documents\GitHub\assignment2-uic-tickets\Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="11370"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="11370" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="サンプル" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="89">
   <si>
     <t>■進級制作　作業報告書</t>
     <rPh sb="1" eb="3">
@@ -3526,6 +3526,38 @@
   </si>
   <si>
     <t>・ゲームマップデザイン２</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>蒲池</t>
+    <rPh sb="0" eb="2">
+      <t>カマチ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・チケットの担当者が未割り当てのままでした。設定してから作業を進めるようにしましょう。</t>
+    <rPh sb="6" eb="9">
+      <t>タントウシャ</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>ミ</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>ワ</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="22" eb="24">
+      <t>セッテイ</t>
+    </rPh>
+    <rPh sb="28" eb="30">
+      <t>サギョウ</t>
+    </rPh>
+    <rPh sb="31" eb="32">
+      <t>スス</t>
+    </rPh>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -4625,8 +4657,12 @@
       <c r="C8" s="14" t="s">
         <v>85</v>
       </c>
-      <c r="D8" s="15"/>
-      <c r="E8" s="13"/>
+      <c r="D8" s="15" t="s">
+        <v>87</v>
+      </c>
+      <c r="E8" s="13" t="s">
+        <v>88</v>
+      </c>
     </row>
     <row r="9" spans="1:6" ht="108" customHeight="1">
       <c r="A9" s="12">

--- a/Reports/07_Takada_Ayumi_作業報告.xlsx
+++ b/Reports/07_Takada_Ayumi_作業報告.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\teacher\Documents\GitHub\assignment2-uic-tickets\Reports\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\student\Documents\assignment2-uic-tickets\Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="91">
   <si>
     <t>■進級制作　作業報告書</t>
     <rPh sb="1" eb="3">
@@ -3558,6 +3558,16 @@
     <rPh sb="31" eb="32">
       <t>スス</t>
     </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・ゲームマップデザイン２
+・コインのプログラム</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・TICKETS - 36 ゲームマップデザイン２ 進行中 → 進行中
+コインのプログラム２</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -4671,7 +4681,9 @@
       <c r="B9" s="14" t="s">
         <v>86</v>
       </c>
-      <c r="C9" s="14"/>
+      <c r="C9" s="14" t="s">
+        <v>90</v>
+      </c>
       <c r="D9" s="15"/>
       <c r="E9" s="13"/>
     </row>
@@ -4679,7 +4691,9 @@
       <c r="A10" s="12">
         <v>46127</v>
       </c>
-      <c r="B10" s="14"/>
+      <c r="B10" s="14" t="s">
+        <v>89</v>
+      </c>
       <c r="C10" s="14"/>
       <c r="D10" s="15"/>
       <c r="E10" s="13"/>

--- a/Reports/07_Takada_Ayumi_作業報告.xlsx
+++ b/Reports/07_Takada_Ayumi_作業報告.xlsx
@@ -3562,12 +3562,12 @@
   </si>
   <si>
     <t>・ゲームマップデザイン２
-・コインのプログラム</t>
+・コインのプログラム２</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>・TICKETS - 36 ゲームマップデザイン２ 進行中 → 進行中
-コインのプログラム２</t>
+・TICKETS - 39 コインのプログラム２ TO-DO</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>

--- a/Reports/07_Takada_Ayumi_作業報告.xlsx
+++ b/Reports/07_Takada_Ayumi_作業報告.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\student\Documents\assignment2-uic-tickets\Reports\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\teacher\Documents\GitHub\assignment2-uic-tickets\Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="93">
   <si>
     <t>■進級制作　作業報告書</t>
     <rPh sb="1" eb="3">
@@ -3568,6 +3568,52 @@
   <si>
     <t>・TICKETS - 36 ゲームマップデザイン２ 進行中 → 進行中
 ・TICKETS - 39 コインのプログラム２ TO-DO</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>蒲池</t>
+    <rPh sb="0" eb="2">
+      <t>カマチ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・4/9に指摘できていなくて申し訳ないのですが、
+　TODO　のままで作業・検討していないのであれば作業報告には入れないようにしましょう。
+　作業検討しているのであれば、進行中にしましょう</t>
+    <rPh sb="5" eb="7">
+      <t>シテキ</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>モウ</t>
+    </rPh>
+    <rPh sb="16" eb="17">
+      <t>ワケ</t>
+    </rPh>
+    <rPh sb="35" eb="37">
+      <t>サギョウ</t>
+    </rPh>
+    <rPh sb="38" eb="40">
+      <t>ケントウ</t>
+    </rPh>
+    <rPh sb="50" eb="52">
+      <t>サギョウ</t>
+    </rPh>
+    <rPh sb="52" eb="54">
+      <t>ホウコク</t>
+    </rPh>
+    <rPh sb="56" eb="57">
+      <t>イ</t>
+    </rPh>
+    <rPh sb="71" eb="73">
+      <t>サギョウ</t>
+    </rPh>
+    <rPh sb="73" eb="75">
+      <t>ケントウ</t>
+    </rPh>
+    <rPh sb="85" eb="88">
+      <t>シンコウチュウ</t>
+    </rPh>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -4684,8 +4730,12 @@
       <c r="C9" s="14" t="s">
         <v>90</v>
       </c>
-      <c r="D9" s="15"/>
-      <c r="E9" s="13"/>
+      <c r="D9" s="15" t="s">
+        <v>91</v>
+      </c>
+      <c r="E9" s="14" t="s">
+        <v>92</v>
+      </c>
     </row>
     <row r="10" spans="1:6" ht="108" customHeight="1">
       <c r="A10" s="12">

--- a/Reports/07_Takada_Ayumi_作業報告.xlsx
+++ b/Reports/07_Takada_Ayumi_作業報告.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\teacher\Documents\GitHub\assignment2-uic-tickets\Reports\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\student\Documents\assignment2-uic-tickets\Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="95">
   <si>
     <t>■進級制作　作業報告書</t>
     <rPh sb="1" eb="3">
@@ -3566,11 +3566,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>・TICKETS - 36 ゲームマップデザイン２ 進行中 → 進行中
-・TICKETS - 39 コインのプログラム２ TO-DO</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>蒲池</t>
     <rPh sb="0" eb="2">
       <t>カマチ</t>
@@ -3614,6 +3609,39 @@
     <rPh sb="85" eb="88">
       <t>シンコウチュウ</t>
     </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・TICKETS - 36 ゲームマップデザイン２ 進行中 → 進行中
+・TICKETS - 39 コインのプログラム２ TO-DO</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・TICKETS - 36 ゲームマップデザイン２ 進行中 → 完了
+・TICKETS - 39 コインのプログラム２ TO-DO → 完了
+・TICKETS - 42 周りの背景の変更作業 TO-DO → 進行中</t>
+    <rPh sb="32" eb="34">
+      <t>カンリョウ</t>
+    </rPh>
+    <rPh sb="68" eb="70">
+      <t>カンリョウ</t>
+    </rPh>
+    <rPh sb="85" eb="86">
+      <t>マワ</t>
+    </rPh>
+    <rPh sb="88" eb="90">
+      <t>ハイケイ</t>
+    </rPh>
+    <rPh sb="91" eb="95">
+      <t>ヘンコウサギョウ</t>
+    </rPh>
+    <rPh sb="104" eb="107">
+      <t>シンコウチュウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・周りの背景の変更作業</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -4728,13 +4756,13 @@
         <v>86</v>
       </c>
       <c r="C9" s="14" t="s">
+        <v>92</v>
+      </c>
+      <c r="D9" s="15" t="s">
         <v>90</v>
       </c>
-      <c r="D9" s="15" t="s">
+      <c r="E9" s="14" t="s">
         <v>91</v>
-      </c>
-      <c r="E9" s="14" t="s">
-        <v>92</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="108" customHeight="1">
@@ -4744,7 +4772,9 @@
       <c r="B10" s="14" t="s">
         <v>89</v>
       </c>
-      <c r="C10" s="14"/>
+      <c r="C10" s="14" t="s">
+        <v>93</v>
+      </c>
       <c r="D10" s="15"/>
       <c r="E10" s="13"/>
     </row>
@@ -4752,7 +4782,9 @@
       <c r="A11" s="12">
         <v>46128</v>
       </c>
-      <c r="B11" s="14"/>
+      <c r="B11" s="14" t="s">
+        <v>94</v>
+      </c>
       <c r="C11" s="14"/>
       <c r="D11" s="15"/>
       <c r="E11" s="13"/>

--- a/Reports/07_Takada_Ayumi_作業報告.xlsx
+++ b/Reports/07_Takada_Ayumi_作業報告.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\student\Documents\assignment2-uic-tickets\Reports\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\teacher\Documents\GitHub\assignment2-uic-tickets\Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="97">
   <si>
     <t>■進級制作　作業報告書</t>
     <rPh sb="1" eb="3">
@@ -3642,6 +3642,47 @@
   </si>
   <si>
     <t>・周りの背景の変更作業</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>蒲池</t>
+    <rPh sb="0" eb="2">
+      <t>カマチ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・TICKETS - 42　はかなり大枠の作業になってしまっているので、やることが具体的になったらサブタスクに分けるか、チケットの詳細を具体的な内容に書き換えるようにしてください。</t>
+    <rPh sb="18" eb="20">
+      <t>オオワク</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>サギョウ</t>
+    </rPh>
+    <rPh sb="41" eb="44">
+      <t>グタイテキ</t>
+    </rPh>
+    <rPh sb="55" eb="56">
+      <t>ワ</t>
+    </rPh>
+    <rPh sb="65" eb="67">
+      <t>ショウサイ</t>
+    </rPh>
+    <rPh sb="68" eb="70">
+      <t>グタイ</t>
+    </rPh>
+    <rPh sb="70" eb="71">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="72" eb="74">
+      <t>ナイヨウ</t>
+    </rPh>
+    <rPh sb="75" eb="76">
+      <t>カ</t>
+    </rPh>
+    <rPh sb="77" eb="78">
+      <t>カ</t>
+    </rPh>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -4775,8 +4816,12 @@
       <c r="C10" s="14" t="s">
         <v>93</v>
       </c>
-      <c r="D10" s="15"/>
-      <c r="E10" s="13"/>
+      <c r="D10" s="15" t="s">
+        <v>95</v>
+      </c>
+      <c r="E10" s="13" t="s">
+        <v>96</v>
+      </c>
     </row>
     <row r="11" spans="1:6" ht="108" customHeight="1">
       <c r="A11" s="12">

--- a/Reports/07_Takada_Ayumi_作業報告.xlsx
+++ b/Reports/07_Takada_Ayumi_作業報告.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\teacher\Documents\GitHub\assignment2-uic-tickets\Reports\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\student\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="99">
   <si>
     <t>■進級制作　作業報告書</t>
     <rPh sb="1" eb="3">
@@ -3682,6 +3682,30 @@
     </rPh>
     <rPh sb="77" eb="78">
       <t>カ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・スタート画面制作</t>
+    <rPh sb="5" eb="9">
+      <t>ガメンセイサク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・TICKETS - 42 周りの背景の変更作業 進行中 → 完了
+・TICKETS - 47 スタート画面制作 TO-DO → 進行中</t>
+    <rPh sb="31" eb="33">
+      <t>カンリョウ</t>
+    </rPh>
+    <rPh sb="52" eb="54">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="54" eb="56">
+      <t>セイサク</t>
+    </rPh>
+    <rPh sb="65" eb="68">
+      <t>シンコウチュウ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -4830,7 +4854,9 @@
       <c r="B11" s="14" t="s">
         <v>94</v>
       </c>
-      <c r="C11" s="14"/>
+      <c r="C11" s="14" t="s">
+        <v>98</v>
+      </c>
       <c r="D11" s="15"/>
       <c r="E11" s="13"/>
     </row>
@@ -4838,7 +4864,9 @@
       <c r="A12" s="12">
         <v>46129</v>
       </c>
-      <c r="B12" s="14"/>
+      <c r="B12" s="14" t="s">
+        <v>97</v>
+      </c>
       <c r="C12" s="14"/>
       <c r="D12" s="15"/>
       <c r="E12" s="13"/>

--- a/Reports/07_Takada_Ayumi_作業報告.xlsx
+++ b/Reports/07_Takada_Ayumi_作業報告.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\student\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\teacher\Documents\GitHub\assignment2-uic-tickets\Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="101">
   <si>
     <t>■進級制作　作業報告書</t>
     <rPh sb="1" eb="3">
@@ -3706,6 +3706,42 @@
     </rPh>
     <rPh sb="65" eb="68">
       <t>シンコウチュウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>蒲池</t>
+    <rPh sb="0" eb="2">
+      <t>カマチ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・順調に進んでいるようで何よりです。
+・スタート画面制作　もやることが多そうなので、チケット分けを検討してみてください。</t>
+    <rPh sb="1" eb="3">
+      <t>ジュンチョウ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>スス</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>ナニ</t>
+    </rPh>
+    <rPh sb="24" eb="26">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="26" eb="28">
+      <t>セイサク</t>
+    </rPh>
+    <rPh sb="35" eb="36">
+      <t>オオ</t>
+    </rPh>
+    <rPh sb="46" eb="47">
+      <t>ワ</t>
+    </rPh>
+    <rPh sb="49" eb="51">
+      <t>ケントウ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -4857,8 +4893,12 @@
       <c r="C11" s="14" t="s">
         <v>98</v>
       </c>
-      <c r="D11" s="15"/>
-      <c r="E11" s="13"/>
+      <c r="D11" s="15" t="s">
+        <v>99</v>
+      </c>
+      <c r="E11" s="14" t="s">
+        <v>100</v>
+      </c>
     </row>
     <row r="12" spans="1:6" ht="108" customHeight="1">
       <c r="A12" s="12">

--- a/Reports/07_Takada_Ayumi_作業報告.xlsx
+++ b/Reports/07_Takada_Ayumi_作業報告.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\teacher\Documents\GitHub\assignment2-uic-tickets\Reports\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\student\Documents\assignment2-uic-tickets\Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="103">
   <si>
     <t>■進級制作　作業報告書</t>
     <rPh sb="1" eb="3">
@@ -3742,6 +3742,49 @@
     </rPh>
     <rPh sb="49" eb="51">
       <t>ケントウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・町中にゴミ箱の配置</t>
+    <rPh sb="1" eb="3">
+      <t>マチナカ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>バコ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>ハイチ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・TICKETS - 47 スタート画面制作 進行中 → 完了
+・TICKETS - 50 ゲーム内UIの制作 TO-DO → 完了
+・TICKETS - 59 ゴミ箱の設置 TO-DO → 進行中</t>
+    <rPh sb="18" eb="20">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>セイサク</t>
+    </rPh>
+    <rPh sb="23" eb="26">
+      <t>シンコウチュウ</t>
+    </rPh>
+    <rPh sb="29" eb="31">
+      <t>カンリョウ</t>
+    </rPh>
+    <rPh sb="49" eb="50">
+      <t>ナイ</t>
+    </rPh>
+    <rPh sb="53" eb="55">
+      <t>セイサク</t>
+    </rPh>
+    <rPh sb="83" eb="84">
+      <t>バコ</t>
+    </rPh>
+    <rPh sb="85" eb="87">
+      <t>セッチ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -4907,7 +4950,9 @@
       <c r="B12" s="14" t="s">
         <v>97</v>
       </c>
-      <c r="C12" s="14"/>
+      <c r="C12" s="14" t="s">
+        <v>102</v>
+      </c>
       <c r="D12" s="15"/>
       <c r="E12" s="13"/>
       <c r="F12" t="s">
@@ -4915,8 +4960,12 @@
       </c>
     </row>
     <row r="13" spans="1:6" ht="108" customHeight="1">
-      <c r="A13" s="12"/>
-      <c r="B13" s="14"/>
+      <c r="A13" s="12">
+        <v>46132</v>
+      </c>
+      <c r="B13" s="14" t="s">
+        <v>101</v>
+      </c>
       <c r="C13" s="14"/>
       <c r="D13" s="15"/>
       <c r="E13" s="13"/>

--- a/Reports/07_Takada_Ayumi_作業報告.xlsx
+++ b/Reports/07_Takada_Ayumi_作業報告.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\student\Documents\assignment2-uic-tickets\Reports\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\teacher\Documents\GitHub\assignment2-uic-tickets\Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="105">
   <si>
     <t>■進級制作　作業報告書</t>
     <rPh sb="1" eb="3">
@@ -3785,6 +3785,35 @@
     </rPh>
     <rPh sb="85" eb="87">
       <t>セッチ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>蒲池</t>
+    <rPh sb="0" eb="2">
+      <t>カマチ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・ゴミ箱の配置はゲームの肝になるので、しっかり調整できるように作れると良いですね。</t>
+    <rPh sb="3" eb="4">
+      <t>バコ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>ハイチ</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>キモ</t>
+    </rPh>
+    <rPh sb="23" eb="25">
+      <t>チョウセイ</t>
+    </rPh>
+    <rPh sb="31" eb="32">
+      <t>ツク</t>
+    </rPh>
+    <rPh sb="35" eb="36">
+      <t>イ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -4953,8 +4982,12 @@
       <c r="C12" s="14" t="s">
         <v>102</v>
       </c>
-      <c r="D12" s="15"/>
-      <c r="E12" s="13"/>
+      <c r="D12" s="15" t="s">
+        <v>103</v>
+      </c>
+      <c r="E12" s="13" t="s">
+        <v>104</v>
+      </c>
       <c r="F12" t="s">
         <v>81</v>
       </c>

--- a/Reports/07_Takada_Ayumi_作業報告.xlsx
+++ b/Reports/07_Takada_Ayumi_作業報告.xlsx
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="106">
   <si>
     <t>■進級制作　作業報告書</t>
     <rPh sb="1" eb="3">
@@ -3785,6 +3785,34 @@
     </rPh>
     <rPh sb="85" eb="87">
       <t>セッチ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・ゴミ箱の配置はゲームの肝になるので、しっかり調整できるように作れると良いですね。</t>
+  </si>
+  <si>
+    <t>・町中にゴミ箱の配置
+・カメラ調整</t>
+    <rPh sb="1" eb="3">
+      <t>マチナカ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>バコ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>ハイチ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・TICKETS - 59 ゴミ箱の設置 進行中 → 進行中
+・TICKETS - 69 カメラ調整の改良 TO-DO → 進行中</t>
+    <rPh sb="48" eb="50">
+      <t>チョウセイ</t>
+    </rPh>
+    <rPh sb="51" eb="53">
+      <t>カイリョウ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -4953,8 +4981,12 @@
       <c r="C12" s="14" t="s">
         <v>102</v>
       </c>
-      <c r="D12" s="15"/>
-      <c r="E12" s="13"/>
+      <c r="D12" s="15" t="s">
+        <v>73</v>
+      </c>
+      <c r="E12" s="13" t="s">
+        <v>103</v>
+      </c>
       <c r="F12" t="s">
         <v>81</v>
       </c>
@@ -4966,13 +4998,19 @@
       <c r="B13" s="14" t="s">
         <v>101</v>
       </c>
-      <c r="C13" s="14"/>
+      <c r="C13" s="14" t="s">
+        <v>105</v>
+      </c>
       <c r="D13" s="15"/>
       <c r="E13" s="13"/>
     </row>
     <row r="14" spans="1:6" ht="108" customHeight="1">
-      <c r="A14" s="12"/>
-      <c r="B14" s="14"/>
+      <c r="A14" s="12">
+        <v>46133</v>
+      </c>
+      <c r="B14" s="14" t="s">
+        <v>104</v>
+      </c>
       <c r="C14" s="14"/>
       <c r="D14" s="15"/>
       <c r="E14" s="13"/>

--- a/Reports/07_Takada_Ayumi_作業報告.xlsx
+++ b/Reports/07_Takada_Ayumi_作業報告.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="11370" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="11370"/>
   </bookViews>
   <sheets>
     <sheet name="サンプル" sheetId="1" r:id="rId1"/>
@@ -4278,6 +4278,9 @@
       </c>
     </row>
     <row r="2" spans="1:5">
+      <c r="A2">
+        <v>1</v>
+      </c>
       <c r="B2" t="s">
         <v>77</v>
       </c>

--- a/Reports/07_Takada_Ayumi_作業報告.xlsx
+++ b/Reports/07_Takada_Ayumi_作業報告.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="11370"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="11370" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="サンプル" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="108">
   <si>
     <t>■進級制作　作業報告書</t>
     <rPh sb="1" eb="3">
@@ -3813,6 +3813,62 @@
     </rPh>
     <rPh sb="51" eb="53">
       <t>カイリョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・TICKETS - 59 ゴミ箱の設置(10個) 進行中 → 完了
+・TICKETS - 68 自販機の設置(23個→13個) TO-DO → 完了
+・TICKETS - 69 カメラ処理の改良 進行中 → 完了
+・TICKETS - 72 缶がゴミ箱に近づいたときだけ光の柱が出てくるようになる TO-DO → 完了</t>
+    <rPh sb="23" eb="24">
+      <t>コ</t>
+    </rPh>
+    <rPh sb="32" eb="34">
+      <t>カンリョウ</t>
+    </rPh>
+    <rPh sb="49" eb="52">
+      <t>ジハンキ</t>
+    </rPh>
+    <rPh sb="62" eb="63">
+      <t>コ</t>
+    </rPh>
+    <rPh sb="93" eb="95">
+      <t>ショリ</t>
+    </rPh>
+    <rPh sb="96" eb="98">
+      <t>カイリョウ</t>
+    </rPh>
+    <rPh sb="99" eb="102">
+      <t>シンコウチュウ</t>
+    </rPh>
+    <rPh sb="122" eb="123">
+      <t>カン</t>
+    </rPh>
+    <rPh sb="126" eb="127">
+      <t>バコ</t>
+    </rPh>
+    <rPh sb="128" eb="129">
+      <t>チカ</t>
+    </rPh>
+    <rPh sb="136" eb="137">
+      <t>ヒカリ</t>
+    </rPh>
+    <rPh sb="138" eb="139">
+      <t>ハシラ</t>
+    </rPh>
+    <rPh sb="140" eb="141">
+      <t>デ</t>
+    </rPh>
+    <rPh sb="158" eb="160">
+      <t>カンリョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・トータルスコアの計算プログラム</t>
+    <rPh sb="9" eb="11">
+      <t>ケイサン</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -5014,26 +5070,36 @@
       <c r="B14" s="14" t="s">
         <v>104</v>
       </c>
-      <c r="C14" s="14"/>
+      <c r="C14" s="14" t="s">
+        <v>106</v>
+      </c>
       <c r="D14" s="15"/>
       <c r="E14" s="13"/>
     </row>
     <row r="15" spans="1:6" ht="108" customHeight="1">
-      <c r="A15" s="12"/>
-      <c r="B15" s="14"/>
+      <c r="A15" s="12">
+        <v>46134</v>
+      </c>
+      <c r="B15" s="14" t="s">
+        <v>107</v>
+      </c>
       <c r="C15" s="14"/>
       <c r="D15" s="15"/>
       <c r="E15" s="13"/>
     </row>
     <row r="16" spans="1:6" ht="108" customHeight="1">
-      <c r="A16" s="12"/>
+      <c r="A16" s="12">
+        <v>46135</v>
+      </c>
       <c r="B16" s="14"/>
       <c r="C16" s="14"/>
       <c r="D16" s="15"/>
       <c r="E16" s="13"/>
     </row>
     <row r="17" spans="1:5" ht="108" customHeight="1">
-      <c r="A17" s="12"/>
+      <c r="A17" s="12">
+        <v>46136</v>
+      </c>
       <c r="B17" s="14"/>
       <c r="C17" s="14"/>
       <c r="D17" s="15"/>

--- a/Reports/07_Takada_Ayumi_作業報告.xlsx
+++ b/Reports/07_Takada_Ayumi_作業報告.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="11370" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="11370"/>
   </bookViews>
   <sheets>
     <sheet name="サンプル" sheetId="1" r:id="rId1"/>
@@ -4334,9 +4334,6 @@
       </c>
     </row>
     <row r="2" spans="1:5">
-      <c r="A2">
-        <v>1</v>
-      </c>
       <c r="B2" t="s">
         <v>77</v>
       </c>

--- a/Reports/07_Takada_Ayumi_作業報告.xlsx
+++ b/Reports/07_Takada_Ayumi_作業報告.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="11370"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="11370" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="サンプル" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="110">
   <si>
     <t>■進級制作　作業報告書</t>
     <rPh sb="1" eb="3">
@@ -3870,6 +3870,31 @@
     <rPh sb="9" eb="11">
       <t>ケイサン</t>
     </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・TICKETS - 75 ゴミ箱のスコアの見直し TO-DO → 完了
+・TICKETS - 77 ハイスコアの取得 TO-DO → 完了
+・TICKETS - 78 シャカシャカゲージの作成 TO-DO → 進行中</t>
+    <rPh sb="16" eb="17">
+      <t>バコ</t>
+    </rPh>
+    <rPh sb="22" eb="24">
+      <t>ミナオ</t>
+    </rPh>
+    <rPh sb="57" eb="59">
+      <t>シュトク</t>
+    </rPh>
+    <rPh sb="95" eb="97">
+      <t>サクセイ</t>
+    </rPh>
+    <rPh sb="106" eb="109">
+      <t>シンコウチュウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・シャカシャカゲージの作成 など</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -5080,7 +5105,9 @@
       <c r="B15" s="14" t="s">
         <v>107</v>
       </c>
-      <c r="C15" s="14"/>
+      <c r="C15" s="14" t="s">
+        <v>108</v>
+      </c>
       <c r="D15" s="15"/>
       <c r="E15" s="13"/>
     </row>
@@ -5088,7 +5115,9 @@
       <c r="A16" s="12">
         <v>46135</v>
       </c>
-      <c r="B16" s="14"/>
+      <c r="B16" s="14" t="s">
+        <v>109</v>
+      </c>
       <c r="C16" s="14"/>
       <c r="D16" s="15"/>
       <c r="E16" s="13"/>

--- a/Reports/07_Takada_Ayumi_作業報告.xlsx
+++ b/Reports/07_Takada_Ayumi_作業報告.xlsx
@@ -5,11 +5,11 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\student\Documents\assignment2-uic-tickets\Reports\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\teacher\Documents\GitHub\assignment2-uic-tickets\Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="11370"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="11370" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="サンプル" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="110">
   <si>
     <t>■進級制作　作業報告書</t>
     <rPh sb="1" eb="3">
@@ -3869,6 +3869,29 @@
     <t>・トータルスコアの計算プログラム</t>
     <rPh sb="9" eb="11">
       <t>ケイサン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>蒲池</t>
+    <rPh sb="0" eb="2">
+      <t>カマチ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・進捗と作業予定の記載をお願いします。</t>
+    <rPh sb="1" eb="3">
+      <t>シンチョク</t>
+    </rPh>
+    <rPh sb="4" eb="8">
+      <t>サギョウヨテイ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>キサイ</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>ネガ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -5081,8 +5104,12 @@
         <v>107</v>
       </c>
       <c r="C15" s="14"/>
-      <c r="D15" s="15"/>
-      <c r="E15" s="13"/>
+      <c r="D15" s="15" t="s">
+        <v>108</v>
+      </c>
+      <c r="E15" s="13" t="s">
+        <v>109</v>
+      </c>
     </row>
     <row r="16" spans="1:6" ht="108" customHeight="1">
       <c r="A16" s="12">

--- a/Reports/07_Takada_Ayumi_作業報告.xlsx
+++ b/Reports/07_Takada_Ayumi_作業報告.xlsx
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="112">
   <si>
     <t>■進級制作　作業報告書</t>
     <rPh sb="1" eb="3">
@@ -3894,7 +3894,50 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
+    <t>・TICKETS - 75 ゴミ箱のスコアの見直し 完了 → 進行中（ゴミ箱スコアの大きさ変更など）
+・TICKETS - 78 シャカシャカゲージの作成 進行中 → 完了
+・TICKETS - 79 コインの上下をなくす TO-DO → 完了</t>
+    <rPh sb="31" eb="34">
+      <t>シンコウチュウ</t>
+    </rPh>
+    <rPh sb="37" eb="38">
+      <t>バコ</t>
+    </rPh>
+    <rPh sb="42" eb="43">
+      <t>オオ</t>
+    </rPh>
+    <rPh sb="45" eb="47">
+      <t>ヘンコウ</t>
+    </rPh>
+    <rPh sb="75" eb="77">
+      <t>サクセイ</t>
+    </rPh>
+    <rPh sb="78" eb="81">
+      <t>シンコウチュウ</t>
+    </rPh>
+    <rPh sb="84" eb="86">
+      <t>カンリョウ</t>
+    </rPh>
+    <rPh sb="105" eb="107">
+      <t>ジョウゲ</t>
+    </rPh>
+    <rPh sb="120" eb="122">
+      <t>カンリョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
     <t>・シャカシャカゲージの作成 など</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・ゴミ箱スコアの見直し</t>
+    <rPh sb="3" eb="4">
+      <t>バコ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>ミナオ</t>
+    </rPh>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -5116,9 +5159,11 @@
         <v>46135</v>
       </c>
       <c r="B16" s="14" t="s">
+        <v>110</v>
+      </c>
+      <c r="C16" s="14" t="s">
         <v>109</v>
       </c>
-      <c r="C16" s="14"/>
       <c r="D16" s="15"/>
       <c r="E16" s="13"/>
     </row>
@@ -5126,7 +5171,9 @@
       <c r="A17" s="12">
         <v>46136</v>
       </c>
-      <c r="B17" s="14"/>
+      <c r="B17" s="14" t="s">
+        <v>111</v>
+      </c>
       <c r="C17" s="14"/>
       <c r="D17" s="15"/>
       <c r="E17" s="13"/>

--- a/Reports/07_Takada_Ayumi_作業報告.xlsx
+++ b/Reports/07_Takada_Ayumi_作業報告.xlsx
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="114">
   <si>
     <t>■進級制作　作業報告書</t>
     <rPh sb="1" eb="3">
@@ -3937,6 +3937,39 @@
     </rPh>
     <rPh sb="8" eb="10">
       <t>ミナオ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・TICKETS - 75 ゴミ箱のスコアの見直し 進行中 → 完了（ゴミ箱の判定の調整も）
+・TICKETS - 82 ドリンクの残り時間のタイマーUI TO-DO → 完了</t>
+    <rPh sb="32" eb="34">
+      <t>カンリョウ</t>
+    </rPh>
+    <rPh sb="37" eb="38">
+      <t>バコ</t>
+    </rPh>
+    <rPh sb="39" eb="41">
+      <t>ハンテイ</t>
+    </rPh>
+    <rPh sb="42" eb="44">
+      <t>チョウセイ</t>
+    </rPh>
+    <rPh sb="66" eb="67">
+      <t>ノコ</t>
+    </rPh>
+    <rPh sb="68" eb="70">
+      <t>ジカン</t>
+    </rPh>
+    <rPh sb="86" eb="88">
+      <t>カンリョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>β版</t>
+    <rPh sb="1" eb="2">
+      <t>バン</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -5167,116 +5200,121 @@
       <c r="D16" s="15"/>
       <c r="E16" s="13"/>
     </row>
-    <row r="17" spans="1:5" ht="108" customHeight="1">
+    <row r="17" spans="1:6" ht="108" customHeight="1">
       <c r="A17" s="12">
         <v>46136</v>
       </c>
       <c r="B17" s="14" t="s">
         <v>111</v>
       </c>
-      <c r="C17" s="14"/>
+      <c r="C17" s="14" t="s">
+        <v>112</v>
+      </c>
       <c r="D17" s="15"/>
       <c r="E17" s="13"/>
-    </row>
-    <row r="18" spans="1:5" ht="108" customHeight="1">
+      <c r="F17" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" ht="108" customHeight="1">
       <c r="A18" s="12"/>
       <c r="B18" s="14"/>
       <c r="C18" s="14"/>
       <c r="D18" s="15"/>
       <c r="E18" s="13"/>
     </row>
-    <row r="19" spans="1:5" ht="108" customHeight="1">
+    <row r="19" spans="1:6" ht="108" customHeight="1">
       <c r="A19" s="12"/>
       <c r="B19" s="14"/>
       <c r="C19" s="14"/>
       <c r="D19" s="15"/>
       <c r="E19" s="13"/>
     </row>
-    <row r="20" spans="1:5" ht="108" customHeight="1">
+    <row r="20" spans="1:6" ht="108" customHeight="1">
       <c r="A20" s="12"/>
       <c r="B20" s="14"/>
       <c r="C20" s="14"/>
       <c r="D20" s="15"/>
       <c r="E20" s="13"/>
     </row>
-    <row r="21" spans="1:5" ht="108" customHeight="1">
+    <row r="21" spans="1:6" ht="108" customHeight="1">
       <c r="A21" s="12"/>
       <c r="B21" s="14"/>
       <c r="C21" s="14"/>
       <c r="D21" s="15"/>
       <c r="E21" s="13"/>
     </row>
-    <row r="22" spans="1:5" ht="108" customHeight="1">
+    <row r="22" spans="1:6" ht="108" customHeight="1">
       <c r="A22" s="12"/>
       <c r="B22" s="14"/>
       <c r="C22" s="14"/>
       <c r="D22" s="15"/>
       <c r="E22" s="13"/>
     </row>
-    <row r="23" spans="1:5" ht="108" customHeight="1">
+    <row r="23" spans="1:6" ht="108" customHeight="1">
       <c r="A23" s="12"/>
       <c r="B23" s="16"/>
       <c r="C23" s="14"/>
       <c r="D23" s="15"/>
       <c r="E23" s="13"/>
     </row>
-    <row r="24" spans="1:5" ht="108" customHeight="1">
+    <row r="24" spans="1:6" ht="108" customHeight="1">
       <c r="A24" s="12"/>
       <c r="B24" s="16"/>
       <c r="C24" s="14"/>
       <c r="D24" s="15"/>
       <c r="E24" s="13"/>
     </row>
-    <row r="25" spans="1:5" ht="108" customHeight="1">
+    <row r="25" spans="1:6" ht="108" customHeight="1">
       <c r="A25" s="12"/>
       <c r="B25" s="16"/>
       <c r="C25" s="14"/>
       <c r="D25" s="15"/>
       <c r="E25" s="13"/>
     </row>
-    <row r="26" spans="1:5" ht="108" customHeight="1">
+    <row r="26" spans="1:6" ht="108" customHeight="1">
       <c r="A26" s="12"/>
       <c r="B26" s="16"/>
       <c r="C26" s="14"/>
       <c r="D26" s="15"/>
       <c r="E26" s="13"/>
     </row>
-    <row r="27" spans="1:5" ht="108" customHeight="1">
+    <row r="27" spans="1:6" ht="108" customHeight="1">
       <c r="A27" s="12"/>
       <c r="B27" s="16"/>
       <c r="C27" s="14"/>
       <c r="D27" s="15"/>
       <c r="E27" s="13"/>
     </row>
-    <row r="28" spans="1:5" ht="108" customHeight="1">
+    <row r="28" spans="1:6" ht="108" customHeight="1">
       <c r="A28" s="12"/>
       <c r="B28" s="16"/>
       <c r="C28" s="14"/>
       <c r="D28" s="15"/>
       <c r="E28" s="13"/>
     </row>
-    <row r="29" spans="1:5" ht="108" customHeight="1">
+    <row r="29" spans="1:6" ht="108" customHeight="1">
       <c r="A29" s="12"/>
       <c r="B29" s="16"/>
       <c r="C29" s="14"/>
       <c r="D29" s="15"/>
       <c r="E29" s="13"/>
     </row>
-    <row r="30" spans="1:5" ht="108" customHeight="1">
+    <row r="30" spans="1:6" ht="108" customHeight="1">
       <c r="A30" s="12"/>
       <c r="B30" s="16"/>
       <c r="C30" s="14"/>
       <c r="D30" s="15"/>
       <c r="E30" s="13"/>
     </row>
-    <row r="31" spans="1:5" ht="108" customHeight="1">
+    <row r="31" spans="1:6" ht="108" customHeight="1">
       <c r="A31" s="12"/>
       <c r="B31" s="16"/>
       <c r="C31" s="14"/>
       <c r="D31" s="15"/>
       <c r="E31" s="13"/>
     </row>
-    <row r="32" spans="1:5" ht="108" customHeight="1">
+    <row r="32" spans="1:6" ht="108" customHeight="1">
       <c r="A32" s="12"/>
       <c r="B32" s="16"/>
       <c r="C32" s="14"/>

--- a/Reports/07_Takada_Ayumi_作業報告.xlsx
+++ b/Reports/07_Takada_Ayumi_作業報告.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\student\Documents\assignment2-uic-tickets\Reports\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\teacher\Documents\GitHub\assignment2-uic-tickets\Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="116">
   <si>
     <t>■進級制作　作業報告書</t>
     <rPh sb="1" eb="3">
@@ -3970,6 +3970,26 @@
     <t>β版</t>
     <rPh sb="1" eb="2">
       <t>バン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>蒲池</t>
+    <rPh sb="0" eb="2">
+      <t>カマチ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・作業予定の記載をお願いします。</t>
+    <rPh sb="1" eb="5">
+      <t>サギョウヨテイ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>キサイ</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>ネガ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -5210,8 +5230,12 @@
       <c r="C17" s="14" t="s">
         <v>112</v>
       </c>
-      <c r="D17" s="15"/>
-      <c r="E17" s="13"/>
+      <c r="D17" s="15" t="s">
+        <v>114</v>
+      </c>
+      <c r="E17" s="13" t="s">
+        <v>115</v>
+      </c>
       <c r="F17" t="s">
         <v>113</v>
       </c>

--- a/Reports/07_Takada_Ayumi_作業報告.xlsx
+++ b/Reports/07_Takada_Ayumi_作業報告.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\teacher\Documents\GitHub\assignment2-uic-tickets\Reports\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\student\Documents\assignment2-uic-tickets\Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="163" uniqueCount="119">
   <si>
     <t>■進級制作　作業報告書</t>
     <rPh sb="1" eb="3">
@@ -3990,6 +3990,40 @@
     </rPh>
     <rPh sb="10" eb="11">
       <t>ネガ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・NPCの配置</t>
+    <rPh sb="5" eb="7">
+      <t>ハイチ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・すべてのごみ箱を光らせる関数
+・コインの獲得範囲の上昇の関数</t>
+    <rPh sb="7" eb="8">
+      <t>バコ</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>ヒカ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>カンスウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・TICKETS - 49 NPCの配置(本プロジェクト) TO-DO → 進行中</t>
+    <rPh sb="18" eb="20">
+      <t>ハイチ</t>
+    </rPh>
+    <rPh sb="21" eb="22">
+      <t>ホン</t>
+    </rPh>
+    <rPh sb="38" eb="41">
+      <t>シンコウチュウ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -5241,15 +5275,25 @@
       </c>
     </row>
     <row r="18" spans="1:6" ht="108" customHeight="1">
-      <c r="A18" s="12"/>
-      <c r="B18" s="14"/>
-      <c r="C18" s="14"/>
+      <c r="A18" s="12">
+        <v>46139</v>
+      </c>
+      <c r="B18" s="14" t="s">
+        <v>116</v>
+      </c>
+      <c r="C18" s="14" t="s">
+        <v>118</v>
+      </c>
       <c r="D18" s="15"/>
       <c r="E18" s="13"/>
     </row>
     <row r="19" spans="1:6" ht="108" customHeight="1">
-      <c r="A19" s="12"/>
-      <c r="B19" s="14"/>
+      <c r="A19" s="12">
+        <v>46140</v>
+      </c>
+      <c r="B19" s="14" t="s">
+        <v>117</v>
+      </c>
       <c r="C19" s="14"/>
       <c r="D19" s="15"/>
       <c r="E19" s="13"/>

--- a/Reports/07_Takada_Ayumi_作業報告.xlsx
+++ b/Reports/07_Takada_Ayumi_作業報告.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="11370" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="11370"/>
   </bookViews>
   <sheets>
     <sheet name="サンプル" sheetId="1" r:id="rId1"/>
@@ -4489,6 +4489,9 @@
       </c>
     </row>
     <row r="2" spans="1:5">
+      <c r="A2">
+        <v>1</v>
+      </c>
       <c r="B2" t="s">
         <v>77</v>
       </c>

--- a/Reports/07_Takada_Ayumi_作業報告.xlsx
+++ b/Reports/07_Takada_Ayumi_作業報告.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="11370"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="11370" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="サンプル" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="163" uniqueCount="119">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="120">
   <si>
     <t>■進級制作　作業報告書</t>
     <rPh sb="1" eb="3">
@@ -4025,6 +4025,13 @@
     <rPh sb="38" eb="41">
       <t>シンコウチュウ</t>
     </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・TICKETS - 88 すべてのごみ箱を光らせる関数 TO-DO → 完了
+・TICKETS - 89 コインの獲得範囲の上昇の関数 TO-DO → 完了
+・TICKETS - 92 制限時間の調整 TO-DO → 完了
+（TICKETS外でシャカシャカゲージ消費時に1で止まる不具合の修正も）</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -5297,7 +5304,9 @@
       <c r="B19" s="14" t="s">
         <v>117</v>
       </c>
-      <c r="C19" s="14"/>
+      <c r="C19" s="14" t="s">
+        <v>119</v>
+      </c>
       <c r="D19" s="15"/>
       <c r="E19" s="13"/>
     </row>

--- a/Reports/07_Takada_Ayumi_作業報告.xlsx
+++ b/Reports/07_Takada_Ayumi_作業報告.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\student\Documents\assignment2-uic-tickets\Reports\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\teacher\Documents\GitHub\assignment2-uic-tickets\Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="122">
   <si>
     <t>■進級制作　作業報告書</t>
     <rPh sb="1" eb="3">
@@ -4032,6 +4032,20 @@
 ・TICKETS - 89 コインの獲得範囲の上昇の関数 TO-DO → 完了
 ・TICKETS - 92 制限時間の調整 TO-DO → 完了
 （TICKETS外でシャカシャカゲージ消費時に1で止まる不具合の修正も）</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>蒲池</t>
+    <rPh sb="0" eb="2">
+      <t>カマチ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>作業報告と翌日の作業予定の記載をお願いします。</t>
+    <rPh sb="0" eb="4">
+      <t>サギョウホウコク</t>
+    </rPh>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -5307,8 +5321,12 @@
       <c r="C19" s="14" t="s">
         <v>119</v>
       </c>
-      <c r="D19" s="15"/>
-      <c r="E19" s="13"/>
+      <c r="D19" s="15" t="s">
+        <v>120</v>
+      </c>
+      <c r="E19" s="13" t="s">
+        <v>121</v>
+      </c>
     </row>
     <row r="20" spans="1:6" ht="108" customHeight="1">
       <c r="A20" s="12"/>

--- a/Reports/07_Takada_Ayumi_作業報告.xlsx
+++ b/Reports/07_Takada_Ayumi_作業報告.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="11370" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="11370" firstSheet="1" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="サンプル" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="124">
   <si>
     <t>■進級制作　作業報告書</t>
     <rPh sb="1" eb="3">
@@ -4032,6 +4032,30 @@
 ・TICKETS - 89 コインの獲得範囲の上昇の関数 TO-DO → 完了
 ・TICKETS - 92 制限時間の調整 TO-DO → 完了
 （TICKETS外でシャカシャカゲージ消費時に1で止まる不具合の修正も）</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>蒲池</t>
+  </si>
+  <si>
+    <t>作業報告と翌日の作業予定の記載をお願いします。</t>
+  </si>
+  <si>
+    <t>・車の配置</t>
+    <rPh sb="1" eb="2">
+      <t>クルマ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ハイチ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・TICKETS - 86 車の配置(案)(本プロジェクト) 進行中 → 完了
+・TICKETS - 96 発表のプレゼンテーション作成 TO-DO → 完了</t>
+    <rPh sb="31" eb="34">
+      <t>シンコウチュウ</t>
+    </rPh>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -5307,13 +5331,23 @@
       <c r="C19" s="14" t="s">
         <v>119</v>
       </c>
-      <c r="D19" s="15"/>
-      <c r="E19" s="13"/>
+      <c r="D19" s="15" t="s">
+        <v>120</v>
+      </c>
+      <c r="E19" s="13" t="s">
+        <v>121</v>
+      </c>
     </row>
     <row r="20" spans="1:6" ht="108" customHeight="1">
-      <c r="A20" s="12"/>
-      <c r="B20" s="14"/>
-      <c r="C20" s="14"/>
+      <c r="A20" s="12">
+        <v>46149</v>
+      </c>
+      <c r="B20" s="14" t="s">
+        <v>122</v>
+      </c>
+      <c r="C20" s="14" t="s">
+        <v>123</v>
+      </c>
       <c r="D20" s="15"/>
       <c r="E20" s="13"/>
     </row>

--- a/Reports/07_Takada_Ayumi_作業報告.xlsx
+++ b/Reports/07_Takada_Ayumi_作業報告.xlsx
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="124">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="125">
   <si>
     <t>■進級制作　作業報告書</t>
     <rPh sb="1" eb="3">
@@ -4055,6 +4055,22 @@
 ・TICKETS - 96 発表のプレゼンテーション作成 TO-DO → 完了</t>
     <rPh sb="31" eb="34">
       <t>シンコウチュウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・残り余っている作業を適当に</t>
+    <rPh sb="1" eb="2">
+      <t>ノコ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>アマ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>サギョウ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>テキトウ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -5352,8 +5368,12 @@
       <c r="E20" s="13"/>
     </row>
     <row r="21" spans="1:6" ht="108" customHeight="1">
-      <c r="A21" s="12"/>
-      <c r="B21" s="14"/>
+      <c r="A21" s="12">
+        <v>46150</v>
+      </c>
+      <c r="B21" s="14" t="s">
+        <v>124</v>
+      </c>
       <c r="C21" s="14"/>
       <c r="D21" s="15"/>
       <c r="E21" s="13"/>

--- a/Reports/07_Takada_Ayumi_作業報告.xlsx
+++ b/Reports/07_Takada_Ayumi_作業報告.xlsx
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="122">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="122">
   <si>
     <t>■進級制作　作業報告書</t>
     <rPh sb="1" eb="3">
@@ -5332,8 +5332,12 @@
       <c r="A20" s="12"/>
       <c r="B20" s="14"/>
       <c r="C20" s="14"/>
-      <c r="D20" s="15"/>
-      <c r="E20" s="13"/>
+      <c r="D20" s="15" t="s">
+        <v>73</v>
+      </c>
+      <c r="E20" s="13" t="s">
+        <v>121</v>
+      </c>
     </row>
     <row r="21" spans="1:6" ht="108" customHeight="1">
       <c r="A21" s="12"/>
